--- a/02_加值成品/九上/九上3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-3 能量的轉換與守恆　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上3-3 能量的轉換與守恆　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>能量不生不滅是什麼定律？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>熱</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>光能與熱能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>能量守恆定律</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>熱能散失</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>燈泡把電能轉成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>光能與熱能</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>熱能散失</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>發光</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>電池把化學能轉成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>供電</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>能量轉換總量如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>力學能與熱能</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>食物提供人體什麼能？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>光能與熱能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>化學能</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>營養</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>轉換常有部分能量變成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>熱能散失</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>耗損</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>效率一般小於？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>力學能與熱能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>無法無中生能持續運轉</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>有散失</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>永動機可行嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>總輸入</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>不可行</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>違反守恆</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>太陽能板將光能轉成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>熱能散失</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>能量轉換時常有部分變成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>光能與熱能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>熱</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>總輸入</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>散失</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-3 能量的轉換與守恆　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上3-3 能量的轉換與守恆　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>水力發電能量鏈？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>化學→電→光熱</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>位能→動能→電能</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>轉為聲熱形變等</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>總量守恆只是形式改變</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>手電筒能量轉換？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>化學→電→光熱</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>化學能→熱能→力學能→電能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>水位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>總量守恆只是形式改變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>鏈</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>摩擦生熱是力學能轉？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>熱能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>散失</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>太陽能板把光能轉成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>光能與熱能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不可行</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>發電</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>效率=有用輸出除以？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>力學能與熱能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>總輸入</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>公式</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>汽車引擎化學能主要轉成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>力學能與熱能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>燃燒</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>能量能憑空產生嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>總輸入</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>不可行</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>電熱水器電能轉成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>熱能散失</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>熱能</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>總輸入</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>熱</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>加熱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>電風扇把電能轉成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>熱能散失</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>動能</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>能量守恆定律</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>風力發電把風的動能轉成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>力學能與熱能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-3 能量的轉換與守恆　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上3-3 能量的轉換與守恆　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何任何機器效率都小於100%？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>化學能→熱能→力學能→電能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>化學→電→光熱</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>總有能量以熱等形式散失</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>摩擦轉成熱能散失</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>散失</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用能量守恆說明永動機不可能？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>化學能→力學能與熱能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>無法無中生能持續運轉</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>化學→電→光熱</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>分析燃煤發電的能量轉換鏈？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>化學能→力學能與熱能</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>水位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>轉為聲熱形變等</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>化學能→熱能→力學能→電能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>鏈</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>自由落體最後撞地能量到哪去？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>轉為聲熱形變等</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>化學→電→光熱</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>水位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>無法無中生能持續運轉</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>LED比白熾燈效率高的意義？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>無法無中生能持續運轉</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>化學能→力學能與熱能</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>較多電能轉光、少散熱</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>效率</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>人體吃飯到運動的能量轉換？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>化學→電→光熱</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>化學能→力學能與熱能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>總有能量以熱等形式散失</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>生物</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>能量守恆與力學能守恆差別？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>轉為聲熱形變等</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>總有能量以熱等形式散失</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>前者含所有形式,後者僅力學能且需無摩擦</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>範圍</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何說能量只是轉換不是消耗？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>總量守恆只是形式改變</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>無法無中生能持續運轉</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>較多電能轉光、少散熱</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>總有能量以熱等形式散失</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何滾動的球最終會停下?能量去哪?</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>較多電能轉光、少散熱</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>摩擦轉成熱能散失</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>前者含所有形式,後者僅力學能且需無摩擦</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>化學能→熱能→力學能→電能</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>分析水力發電的能量轉換鏈？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>水位能→動能→電能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>總量守恆只是形式改變</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>較多電能轉光、少散熱</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>鏈</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：能量不會憑空出現也不會憑空消失,這個規律叫做能量守恆定律</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>發光</t>
+          <t>發光：電流通過燈泡後,一部分電能變成光讓我們看見,一部分變成熱</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>供電</t>
+          <t>供電：電池裡儲存的化學能,經過反應轉換成能供電使用的電能</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：不管能量怎麼從一種形式變成另一種,總量加起來都不會改變</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>營養</t>
+          <t>營養：食物裡含有化學能,人體消化後用來提供活動所需的能量</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>耗損</t>
+          <t>耗損：能量轉換過程中,常常會有一部分變成熱能跑掉,不能全部利用</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>有散失</t>
+          <t>有散失：因為轉換時總會損失一些能量變熱,所以效率通常不到百分之百</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>違反守恆</t>
+          <t>違反守恆：永動機需要無中生有製造能量,這違反了能量守恆定律所以做不出來</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：太陽能板利用光電效應,把太陽光的光能直接轉換成電能</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>散失</t>
+          <t>散失：能量在轉換過程中,常因摩擦等因素損耗,有一部分會轉變成熱能散失掉,不會全部變成想要的能量</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：高處的水先具有位能,落下時位能變動能,推動機器再轉成電能</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>鏈</t>
+          <t>鏈：電池的化學能先變成電能,再讓燈泡發光發熱變成光能和熱能</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>散失</t>
+          <t>散失：物體摩擦時,原本的運動能量有一部分轉變成熱能而流失掉</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>發電</t>
+          <t>發電：太陽能板吸收太陽的光能,經過特殊材料轉換成可用的電能</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>公式</t>
+          <t>公式：效率就是真正有用的輸出能量,除以一開始投入的總能量</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>燃燒</t>
+          <t>燃燒：汽油燃燒釋放化學能,一部分變成推動車子的力學能,一部分變成熱能</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：根據能量守恆定律,能量不可能無中生有地被創造出來</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>加熱</t>
+          <t>加熱：電熱水器利用電流通過發熱線圈,把電能轉換成加熱水的熱能</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：電風扇利用馬達,把插座供給的電能轉換成扇葉轉動的動能</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：風力發電機利用風吹動葉片轉動發電機,把風的動能轉換成電能</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>散失</t>
+          <t>散失：機器運轉時零件摩擦、電阻發熱等,總會讓一部分能量變成熱散失掉</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：機器運轉一定會損耗能量,若沒有外部補充能量,根本不可能無中生有一直轉下去</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>鏈</t>
+          <t>鏈：煤炭燃燒先放出化學能變熱能,加熱水產生蒸氣推動渦輪變成力學能,最後發電機轉成電能</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：撞擊瞬間,原本的動能不會消失,而是轉變成聲音、熱、還有物體變形等各種能量</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>效率</t>
+          <t>效率：LED燈把更多電能變成有用的光,浪費在發熱上的能量比較少</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>生物</t>
+          <t>生物：吃下的食物含化學能,身體消化吸收後用來運動,一部分變力學能一部分變體熱</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>範圍</t>
+          <t>範圍：能量守恆包括所有形式的能量,力學能守恆則只限動能和位能,且要求沒有摩擦損耗</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：我們常說耗電耗能,其實能量只是從一種形式變成另一種,總量並沒有真正減少</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：球滾動時受到地面摩擦力和空氣阻力,原本的動能逐漸轉換成熱能散失到環境中,所以球會慢慢停下</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>鏈</t>
+          <t>鏈：高處的水具有位能,水往下流動時位能轉成動能,再推動水輪機帶動發電機,把動能轉換成電能</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-3_三種難度測驗卷.xlsx
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>總輸入</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>熱能散失</t>
+          <t>不可行</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>光能與熱能</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>能量守恆定律</t>
+          <t>電能</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>總輸入</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -803,14 +803,14 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>能量守恆定律</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>力學能與熱能</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>100%</t>
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>無法無中生能持續運轉</t>
+          <t>不可行</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>光能與熱能</t>
+          <t>不可行</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>總輸入</t>
+          <t>化學能</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,22 +1039,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>前者含所有形式,後者僅力學能且需無摩擦</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>化學→電→光熱</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>位能→動能→電能</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>轉為聲熱形變等</t>
-        </is>
-      </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>總量守恆只是形式改變</t>
+          <t>化學能→熱能→力學能→電能</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>化學能</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>化學能</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>不可行</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>光能與熱能</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>化學能</t>
+          <t>能量守恆定律</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>熱能散失</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>總輸入</t>
+          <t>電能</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>熱</t>
+          <t>化學能</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>位能→動能→電能</t>
+          <t>前者含所有形式,後者僅力學能且需無摩擦</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>總量守恆只是形式改變</t>
+          <t>化學能→熱能→力學能→電能</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>較多電能轉光、少散熱</t>
+          <t>摩擦轉成熱能散失</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
